--- a/topic/data/study_dept_bank_type.xlsx
+++ b/topic/data/study_dept_bank_type.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="15225" windowHeight="12150"/>
   </bookViews>
   <sheets>
     <sheet name="study_dept_bank_type" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="508">
   <si>
     <t>id</t>
   </si>
@@ -349,6 +349,33 @@
     <t>综采</t>
   </si>
   <si>
+    <t>320b889bace948a6971b729f2166be2b</t>
+  </si>
+  <si>
+    <t>002002,sgjsjytk,事故警示教育题库</t>
+  </si>
+  <si>
+    <t>c6ae4929743211f08007000c291cdc3b</t>
+  </si>
+  <si>
+    <t>周登辉</t>
+  </si>
+  <si>
+    <t>dbb0079659804e27be0243f7251bd638</t>
+  </si>
+  <si>
+    <t>事故警示教育题库</t>
+  </si>
+  <si>
+    <t>002002</t>
+  </si>
+  <si>
+    <t>18ecf8619cfb48c98c27e19ac704a1a5</t>
+  </si>
+  <si>
+    <t>容大煤业</t>
+  </si>
+  <si>
     <t>001006,aq,安全</t>
   </si>
   <si>
@@ -616,612 +643,612 @@
     <t>001005001</t>
   </si>
   <si>
-    <t>689b511622bb4112bc89ce80baea4b8a</t>
-  </si>
-  <si>
-    <t>002001,ajk,安监科</t>
-  </si>
-  <si>
-    <t>c6ae4929743211f08007000c291cdc3b</t>
-  </si>
-  <si>
-    <t>周登辉</t>
-  </si>
-  <si>
-    <t>dbb0079659804e27be0243f7251bd638</t>
-  </si>
-  <si>
-    <t>安监科</t>
+    <t>694b4c82a36f467882f47695255ec8c9</t>
+  </si>
+  <si>
+    <t>004001,jdys,机电运输</t>
+  </si>
+  <si>
+    <t>da6c0fb8c419c8ab713c01d42a16af80</t>
+  </si>
+  <si>
+    <t>刘新亮</t>
+  </si>
+  <si>
+    <t>004001</t>
+  </si>
+  <si>
+    <t>69cb2b13cc0e4eb09ff94bd478c27d07</t>
+  </si>
+  <si>
+    <t>001010001,xjy,巡检员</t>
+  </si>
+  <si>
+    <t>巡检员</t>
+  </si>
+  <si>
+    <t>001010001</t>
+  </si>
+  <si>
+    <t>6a2bcb33b4b4451a9fd89843bd757d16</t>
+  </si>
+  <si>
+    <t>001005003,fcg,防尘工</t>
+  </si>
+  <si>
+    <t>防尘工</t>
+  </si>
+  <si>
+    <t>001005003</t>
+  </si>
+  <si>
+    <t>6e065fbd142744a299dd2f81c11104a2</t>
+  </si>
+  <si>
+    <t>001009005,ztfjzby,主通风机值班员</t>
+  </si>
+  <si>
+    <t>主通风机值班员</t>
+  </si>
+  <si>
+    <t>001009005</t>
+  </si>
+  <si>
+    <t>72eb04651507425982b21455805f7bda</t>
+  </si>
+  <si>
+    <t>001001013,fbldyscsj,防爆履带运输车司机</t>
+  </si>
+  <si>
+    <t>防爆履带运输车司机</t>
+  </si>
+  <si>
+    <t>001001013</t>
+  </si>
+  <si>
+    <t>7387c44771ef480da14346631d819a6c</t>
+  </si>
+  <si>
+    <t>004010,tdzhzx,调度指挥中心</t>
+  </si>
+  <si>
+    <t>调度指挥中心</t>
+  </si>
+  <si>
+    <t>004010</t>
+  </si>
+  <si>
+    <t>74f751acedd94543b985232b71a9cedf</t>
+  </si>
+  <si>
+    <t>001004008,sbsj,水泵司机</t>
+  </si>
+  <si>
+    <t>水泵司机</t>
+  </si>
+  <si>
+    <t>001004008</t>
+  </si>
+  <si>
+    <t>001010,jkxx,监控信息</t>
+  </si>
+  <si>
+    <t>001010</t>
+  </si>
+  <si>
+    <t>796b8a93c97348bca9a68baff5d80f2e</t>
+  </si>
+  <si>
+    <t>001007005,zdzzby,注氮站值班员</t>
+  </si>
+  <si>
+    <t>注氮站值班员</t>
+  </si>
+  <si>
+    <t>001007005</t>
+  </si>
+  <si>
+    <t>79fad753e9ad478ab2a748224dff0626</t>
+  </si>
+  <si>
+    <t>001003010,jxxlg,井下修理工</t>
+  </si>
+  <si>
+    <t>井下修理工</t>
+  </si>
+  <si>
+    <t>001003010</t>
+  </si>
+  <si>
+    <t>7b2941244c0d40d79a32072613e04a92</t>
+  </si>
+  <si>
+    <t>001005004,glg,管路工</t>
+  </si>
+  <si>
+    <t>管路工</t>
+  </si>
+  <si>
+    <t>001005004</t>
+  </si>
+  <si>
+    <t>7c4c91fd684044c0abd559a53f90fa45</t>
+  </si>
+  <si>
+    <t>001003001,bzz,班组长</t>
+  </si>
+  <si>
+    <t>班组长</t>
+  </si>
+  <si>
+    <t>001003001</t>
+  </si>
+  <si>
+    <t>7c7ff2dd38554a5e9e6db128fc185ec0</t>
+  </si>
+  <si>
+    <t>001009009,kyjsj,空压机司机</t>
+  </si>
+  <si>
+    <t>空压机司机</t>
+  </si>
+  <si>
+    <t>001009009</t>
+  </si>
+  <si>
+    <t>7cdda0d5d9e94298b50d9609aeb05755</t>
+  </si>
+  <si>
+    <t>001001011,zcggtm,综采公共题目</t>
+  </si>
+  <si>
+    <t>综采公共题目</t>
+  </si>
+  <si>
+    <t>001001011</t>
+  </si>
+  <si>
+    <t>7d09702df3bb42f29b3b121ed601497f</t>
+  </si>
+  <si>
+    <t>001009002,glg,管路工</t>
+  </si>
+  <si>
+    <t>001009002</t>
+  </si>
+  <si>
+    <t>7d26296c175349bfad2f30dbbb54b956</t>
+  </si>
+  <si>
+    <t>003003,jjd,掘进队</t>
+  </si>
+  <si>
+    <t>掘进队</t>
+  </si>
+  <si>
+    <t>003003</t>
+  </si>
+  <si>
+    <t>001001,zc,综采</t>
+  </si>
+  <si>
+    <t>001001</t>
+  </si>
+  <si>
+    <t>7ff0bf7a435243dd9739ccb9fcb18cbc</t>
+  </si>
+  <si>
+    <t>001002005,dg,电工</t>
+  </si>
+  <si>
+    <t>电工</t>
+  </si>
+  <si>
+    <t>001002005</t>
+  </si>
+  <si>
+    <t>80604b058c8648738df67ce56f0fc7d6</t>
+  </si>
+  <si>
+    <t>001006001,aqjcy,安全检查员</t>
+  </si>
+  <si>
+    <t>安全检查员</t>
+  </si>
+  <si>
+    <t>001006001</t>
+  </si>
+  <si>
+    <t>82c8f2152f3b4c20a070d38b4140738f</t>
+  </si>
+  <si>
+    <t>001001009,cmgzmdg,采煤工作面电工</t>
+  </si>
+  <si>
+    <t>采煤工作面电工</t>
+  </si>
+  <si>
+    <t>001001009</t>
+  </si>
+  <si>
+    <t>837bd75310534686ae7b3ce10f41944a</t>
+  </si>
+  <si>
+    <t>001004002,dg,电工</t>
+  </si>
+  <si>
+    <t>8444db8183c84e0992587fe9826d1408</t>
+  </si>
+  <si>
+    <t>004009,dzfzsb,地质防治水部</t>
+  </si>
+  <si>
+    <t>地质防治水部</t>
+  </si>
+  <si>
+    <t>004009</t>
+  </si>
+  <si>
+    <t>89e659799124461bb13ed513eb476efc</t>
+  </si>
+  <si>
+    <t>003006,tfd,通风队</t>
+  </si>
+  <si>
+    <t>003006</t>
+  </si>
+  <si>
+    <t>8cffd47e721d42a8969a9fa067ac6cd3</t>
+  </si>
+  <si>
+    <t>004007,ajb,安监部</t>
+  </si>
+  <si>
+    <t>安监部</t>
+  </si>
+  <si>
+    <t>004007</t>
+  </si>
+  <si>
+    <t>8de632e22cb3472586688eff1f184c6a</t>
+  </si>
+  <si>
+    <t>001003003,jxjcg,井下绞车工</t>
+  </si>
+  <si>
+    <t>井下绞车工</t>
+  </si>
+  <si>
+    <t>001003003</t>
+  </si>
+  <si>
+    <t>909366291e5a4893be9e65485985f37e</t>
+  </si>
+  <si>
+    <t>001006002,jkjsy,井口检身员</t>
+  </si>
+  <si>
+    <t>井口检身员</t>
+  </si>
+  <si>
+    <t>001006002</t>
+  </si>
+  <si>
+    <t>96d134115009446bb20ee7c87dcb8e5f</t>
+  </si>
+  <si>
+    <t>001003009,jxxhg,井下信号工</t>
+  </si>
+  <si>
+    <t>井下信号工</t>
+  </si>
+  <si>
+    <t>001003009</t>
+  </si>
+  <si>
+    <t>980acdf782f144bfaf8f43c5690c0975</t>
+  </si>
+  <si>
+    <t>001012,sxstcmthyfzhaqxgsqt,山西省统筹煤炭行业发展和安全新规十七条</t>
+  </si>
+  <si>
+    <t>955bc74530d111f095ae4cd98fac570d</t>
+  </si>
+  <si>
+    <t>高雪云</t>
+  </si>
+  <si>
+    <t>山西省统筹煤炭行业发展和安全新规十七条</t>
+  </si>
+  <si>
+    <t>001012</t>
+  </si>
+  <si>
+    <t>9be00e3bc9ba4a66ac6c38cceb25d5b0</t>
+  </si>
+  <si>
+    <t>001004007,dsssjjxg,带式输送机检修工</t>
+  </si>
+  <si>
+    <t>带式输送机检修工</t>
+  </si>
+  <si>
+    <t>001004007</t>
+  </si>
+  <si>
+    <t>9ee3c5064f3c40d4b5ad91c98d3e1b51</t>
+  </si>
+  <si>
+    <t>004002,yjzhzx,应急指挥中心</t>
+  </si>
+  <si>
+    <t>应急指挥中心</t>
+  </si>
+  <si>
+    <t>004002</t>
+  </si>
+  <si>
+    <t>9f658ca5462d4015827767d7cec720f4</t>
+  </si>
+  <si>
+    <t>004012,ytsfb,一通三防部</t>
+  </si>
+  <si>
+    <t>一通三防部</t>
+  </si>
+  <si>
+    <t>004012</t>
+  </si>
+  <si>
+    <t>a38adf5ae1bc49fea62a9e2c7296615a</t>
+  </si>
+  <si>
+    <t>004006,zhb,综合部</t>
+  </si>
+  <si>
+    <t>综合部</t>
+  </si>
+  <si>
+    <t>004006</t>
+  </si>
+  <si>
+    <t>a4e70c8eee0e40eaaac9368b6aed3d20</t>
+  </si>
+  <si>
+    <t>003004,cmd,采煤队</t>
+  </si>
+  <si>
+    <t>采煤队</t>
+  </si>
+  <si>
+    <t>003004</t>
+  </si>
+  <si>
+    <t>001,xlmy,鑫隆煤业</t>
+  </si>
+  <si>
+    <t>7ee2dcebe020b54bbc9ee4cc15538606</t>
+  </si>
+  <si>
+    <t>胡勤康</t>
+  </si>
+  <si>
+    <t>955bb98030d111f095ae4cd98fac570d</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>a65aa3ea057a4536a883b6b0f264ca34</t>
+  </si>
+  <si>
+    <t>004003,jsb,技术部</t>
+  </si>
+  <si>
+    <t>技术部</t>
+  </si>
+  <si>
+    <t>004003</t>
+  </si>
+  <si>
+    <t>a77ffbda7ed84370aa8a0e619740e01f</t>
+  </si>
+  <si>
+    <t>001001007,cmgzmqmg,采煤工作面清煤工</t>
+  </si>
+  <si>
+    <t>采煤工作面清煤工</t>
+  </si>
+  <si>
+    <t>001001007</t>
+  </si>
+  <si>
+    <t>a7ed97511497410b9c4d54d361143278</t>
+  </si>
+  <si>
+    <t>001001012,wcl8yy fbcyjldszjbycsj,WCL8YY 防爆柴油机履带式支架搬运车司机</t>
+  </si>
+  <si>
+    <t>WCL8YY 防爆柴油机履带式支架搬运车司机</t>
+  </si>
+  <si>
+    <t>001001012</t>
+  </si>
+  <si>
+    <t>a9c9e12f3d344664b58f222019c1b347</t>
+  </si>
+  <si>
+    <t>001002001,bz,班长</t>
+  </si>
+  <si>
+    <t>班长</t>
+  </si>
+  <si>
+    <t>001002001</t>
+  </si>
+  <si>
+    <t>001007,cc,抽采</t>
+  </si>
+  <si>
+    <t>001007</t>
+  </si>
+  <si>
+    <t>ac4085c13f67404799cb2eae64617a3e</t>
+  </si>
+  <si>
+    <t>001005002,wsy,瓦斯员</t>
+  </si>
+  <si>
+    <t>瓦斯员</t>
+  </si>
+  <si>
+    <t>001005002</t>
+  </si>
+  <si>
+    <t>ac43e2c35aba4da6b3398a9fc7de455b</t>
+  </si>
+  <si>
+    <t>001001008,cmgzmzzj、ysjsj,采煤工作面转载机、运输机司机</t>
+  </si>
+  <si>
+    <t>采煤工作面转载机、运输机司机</t>
+  </si>
+  <si>
+    <t>001001008</t>
+  </si>
+  <si>
+    <t>b26cd90198364f09a651458554588911</t>
+  </si>
+  <si>
+    <t>004008,aqjgb,安全监管部</t>
+  </si>
+  <si>
+    <t>安全监管部</t>
+  </si>
+  <si>
+    <t>004008</t>
+  </si>
+  <si>
+    <t>b29bf04cc9904ccabf97cdb75c913b16</t>
+  </si>
+  <si>
+    <t>001003006,jxdqg,井下电钳工</t>
+  </si>
+  <si>
+    <t>井下电钳工</t>
+  </si>
+  <si>
+    <t>001003006</t>
+  </si>
+  <si>
+    <t>001009,dmjdd,地面机电队</t>
+  </si>
+  <si>
+    <t>001009</t>
+  </si>
+  <si>
+    <t>b9f12740934a458c81591c233ec6a46c</t>
+  </si>
+  <si>
+    <t>001009011,fdgjxlg,风动工具修理工</t>
+  </si>
+  <si>
+    <t>风动工具修理工</t>
+  </si>
+  <si>
+    <t>001009011</t>
+  </si>
+  <si>
+    <t>ba158726889b412e9a4083a512e96674</t>
+  </si>
+  <si>
+    <t>003008,aqy,安全员</t>
+  </si>
+  <si>
+    <t>安全员</t>
+  </si>
+  <si>
+    <t>003008</t>
+  </si>
+  <si>
+    <t>001003,ys,运输</t>
+  </si>
+  <si>
+    <t>001003</t>
+  </si>
+  <si>
+    <t>bcf95c5c14d8458bb2e13338c1821e83</t>
+  </si>
+  <si>
+    <t>004004,scjsb,生产技术部</t>
+  </si>
+  <si>
+    <t>生产技术部</t>
+  </si>
+  <si>
+    <t>004004</t>
+  </si>
+  <si>
+    <t>003,hamy,惠安煤业</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>004,mygs,煤业公司</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>c12aa4ec5119436c90caa20d169adeba</t>
+  </si>
+  <si>
+    <t>001002002,jjjsj,掘进机司机</t>
+  </si>
+  <si>
+    <t>掘进机司机</t>
+  </si>
+  <si>
+    <t>001002002</t>
+  </si>
+  <si>
+    <t>c33b9ddeda6141b79bffbb8582a67e4b</t>
+  </si>
+  <si>
+    <t>003009,jkzx,监控中心</t>
+  </si>
+  <si>
+    <t>监控中心</t>
+  </si>
+  <si>
+    <t>003009</t>
+  </si>
+  <si>
+    <t>001005,tf,通风</t>
+  </si>
+  <si>
+    <t>通风</t>
+  </si>
+  <si>
+    <t>001005</t>
+  </si>
+  <si>
+    <t>c5e7563bd6854d338b11021bce1dafa8</t>
+  </si>
+  <si>
+    <t>002001,2026b《zdsgyhpdbz》kstk,2026版《重大事故隐患判定标准》考试题库</t>
+  </si>
+  <si>
+    <t>2026版《重大事故隐患判定标准》考试题库</t>
   </si>
   <si>
     <t>002001</t>
   </si>
   <si>
-    <t>18ecf8619cfb48c98c27e19ac704a1a5</t>
-  </si>
-  <si>
-    <t>容大煤业</t>
-  </si>
-  <si>
-    <t>荣大煤业</t>
-  </si>
-  <si>
-    <t>694b4c82a36f467882f47695255ec8c9</t>
-  </si>
-  <si>
-    <t>004001,jdys,机电运输</t>
-  </si>
-  <si>
-    <t>da6c0fb8c419c8ab713c01d42a16af80</t>
-  </si>
-  <si>
-    <t>刘新亮</t>
-  </si>
-  <si>
-    <t>004001</t>
-  </si>
-  <si>
-    <t>69cb2b13cc0e4eb09ff94bd478c27d07</t>
-  </si>
-  <si>
-    <t>001010001,xjy,巡检员</t>
-  </si>
-  <si>
-    <t>巡检员</t>
-  </si>
-  <si>
-    <t>001010001</t>
-  </si>
-  <si>
-    <t>6a2bcb33b4b4451a9fd89843bd757d16</t>
-  </si>
-  <si>
-    <t>001005003,fcg,防尘工</t>
-  </si>
-  <si>
-    <t>防尘工</t>
-  </si>
-  <si>
-    <t>001005003</t>
-  </si>
-  <si>
-    <t>6e065fbd142744a299dd2f81c11104a2</t>
-  </si>
-  <si>
-    <t>001009005,ztfjzby,主通风机值班员</t>
-  </si>
-  <si>
-    <t>主通风机值班员</t>
-  </si>
-  <si>
-    <t>001009005</t>
-  </si>
-  <si>
-    <t>72eb04651507425982b21455805f7bda</t>
-  </si>
-  <si>
-    <t>001001013,fbldyscsj,防爆履带运输车司机</t>
-  </si>
-  <si>
-    <t>防爆履带运输车司机</t>
-  </si>
-  <si>
-    <t>001001013</t>
-  </si>
-  <si>
-    <t>7387c44771ef480da14346631d819a6c</t>
-  </si>
-  <si>
-    <t>004010,tdzhzx,调度指挥中心</t>
-  </si>
-  <si>
-    <t>调度指挥中心</t>
-  </si>
-  <si>
-    <t>004010</t>
-  </si>
-  <si>
-    <t>74f751acedd94543b985232b71a9cedf</t>
-  </si>
-  <si>
-    <t>001004008,sbsj,水泵司机</t>
-  </si>
-  <si>
-    <t>水泵司机</t>
-  </si>
-  <si>
-    <t>001004008</t>
-  </si>
-  <si>
-    <t>001010,jkxx,监控信息</t>
-  </si>
-  <si>
-    <t>001010</t>
-  </si>
-  <si>
-    <t>796b8a93c97348bca9a68baff5d80f2e</t>
-  </si>
-  <si>
-    <t>001007005,zdzzby,注氮站值班员</t>
-  </si>
-  <si>
-    <t>注氮站值班员</t>
-  </si>
-  <si>
-    <t>001007005</t>
-  </si>
-  <si>
-    <t>79fad753e9ad478ab2a748224dff0626</t>
-  </si>
-  <si>
-    <t>001003010,jxxlg,井下修理工</t>
-  </si>
-  <si>
-    <t>井下修理工</t>
-  </si>
-  <si>
-    <t>001003010</t>
-  </si>
-  <si>
-    <t>7b2941244c0d40d79a32072613e04a92</t>
-  </si>
-  <si>
-    <t>001005004,glg,管路工</t>
-  </si>
-  <si>
-    <t>管路工</t>
-  </si>
-  <si>
-    <t>001005004</t>
-  </si>
-  <si>
-    <t>7c4c91fd684044c0abd559a53f90fa45</t>
-  </si>
-  <si>
-    <t>001003001,bzz,班组长</t>
-  </si>
-  <si>
-    <t>班组长</t>
-  </si>
-  <si>
-    <t>001003001</t>
-  </si>
-  <si>
-    <t>7c7ff2dd38554a5e9e6db128fc185ec0</t>
-  </si>
-  <si>
-    <t>001009009,kyjsj,空压机司机</t>
-  </si>
-  <si>
-    <t>空压机司机</t>
-  </si>
-  <si>
-    <t>001009009</t>
-  </si>
-  <si>
-    <t>7cdda0d5d9e94298b50d9609aeb05755</t>
-  </si>
-  <si>
-    <t>001001011,zcggtm,综采公共题目</t>
-  </si>
-  <si>
-    <t>综采公共题目</t>
-  </si>
-  <si>
-    <t>001001011</t>
-  </si>
-  <si>
-    <t>7d09702df3bb42f29b3b121ed601497f</t>
-  </si>
-  <si>
-    <t>001009002,glg,管路工</t>
-  </si>
-  <si>
-    <t>001009002</t>
-  </si>
-  <si>
-    <t>7d26296c175349bfad2f30dbbb54b956</t>
-  </si>
-  <si>
-    <t>003003,jjd,掘进队</t>
-  </si>
-  <si>
-    <t>掘进队</t>
-  </si>
-  <si>
-    <t>003003</t>
-  </si>
-  <si>
-    <t>001001,zc,综采</t>
-  </si>
-  <si>
-    <t>001001</t>
-  </si>
-  <si>
-    <t>7ff0bf7a435243dd9739ccb9fcb18cbc</t>
-  </si>
-  <si>
-    <t>001002005,dg,电工</t>
-  </si>
-  <si>
-    <t>电工</t>
-  </si>
-  <si>
-    <t>001002005</t>
-  </si>
-  <si>
-    <t>80604b058c8648738df67ce56f0fc7d6</t>
-  </si>
-  <si>
-    <t>001006001,aqjcy,安全检查员</t>
-  </si>
-  <si>
-    <t>安全检查员</t>
-  </si>
-  <si>
-    <t>001006001</t>
-  </si>
-  <si>
-    <t>82c8f2152f3b4c20a070d38b4140738f</t>
-  </si>
-  <si>
-    <t>001001009,cmgzmdg,采煤工作面电工</t>
-  </si>
-  <si>
-    <t>采煤工作面电工</t>
-  </si>
-  <si>
-    <t>001001009</t>
-  </si>
-  <si>
-    <t>837bd75310534686ae7b3ce10f41944a</t>
-  </si>
-  <si>
-    <t>001004002,dg,电工</t>
-  </si>
-  <si>
-    <t>8444db8183c84e0992587fe9826d1408</t>
-  </si>
-  <si>
-    <t>004009,dzfzsb,地质防治水部</t>
-  </si>
-  <si>
-    <t>地质防治水部</t>
-  </si>
-  <si>
-    <t>004009</t>
-  </si>
-  <si>
-    <t>89e659799124461bb13ed513eb476efc</t>
-  </si>
-  <si>
-    <t>003006,tfd,通风队</t>
-  </si>
-  <si>
-    <t>003006</t>
-  </si>
-  <si>
-    <t>8cffd47e721d42a8969a9fa067ac6cd3</t>
-  </si>
-  <si>
-    <t>004007,ajb,安监部</t>
-  </si>
-  <si>
-    <t>安监部</t>
-  </si>
-  <si>
-    <t>004007</t>
-  </si>
-  <si>
-    <t>8de632e22cb3472586688eff1f184c6a</t>
-  </si>
-  <si>
-    <t>001003003,jxjcg,井下绞车工</t>
-  </si>
-  <si>
-    <t>井下绞车工</t>
-  </si>
-  <si>
-    <t>001003003</t>
-  </si>
-  <si>
-    <t>909366291e5a4893be9e65485985f37e</t>
-  </si>
-  <si>
-    <t>001006002,jkjsy,井口检身员</t>
-  </si>
-  <si>
-    <t>井口检身员</t>
-  </si>
-  <si>
-    <t>001006002</t>
-  </si>
-  <si>
-    <t>96d134115009446bb20ee7c87dcb8e5f</t>
-  </si>
-  <si>
-    <t>001003009,jxxhg,井下信号工</t>
-  </si>
-  <si>
-    <t>井下信号工</t>
-  </si>
-  <si>
-    <t>001003009</t>
-  </si>
-  <si>
-    <t>9be00e3bc9ba4a66ac6c38cceb25d5b0</t>
-  </si>
-  <si>
-    <t>001004007,dsssjjxg,带式输送机检修工</t>
-  </si>
-  <si>
-    <t>带式输送机检修工</t>
-  </si>
-  <si>
-    <t>001004007</t>
-  </si>
-  <si>
-    <t>9ee3c5064f3c40d4b5ad91c98d3e1b51</t>
-  </si>
-  <si>
-    <t>004002,yjzhzx,应急指挥中心</t>
-  </si>
-  <si>
-    <t>应急指挥中心</t>
-  </si>
-  <si>
-    <t>004002</t>
-  </si>
-  <si>
-    <t>9f658ca5462d4015827767d7cec720f4</t>
-  </si>
-  <si>
-    <t>004012,ytsfb,一通三防部</t>
-  </si>
-  <si>
-    <t>一通三防部</t>
-  </si>
-  <si>
-    <t>004012</t>
-  </si>
-  <si>
-    <t>a38adf5ae1bc49fea62a9e2c7296615a</t>
-  </si>
-  <si>
-    <t>004006,zhb,综合部</t>
-  </si>
-  <si>
-    <t>综合部</t>
-  </si>
-  <si>
-    <t>004006</t>
-  </si>
-  <si>
-    <t>a4e70c8eee0e40eaaac9368b6aed3d20</t>
-  </si>
-  <si>
-    <t>003004,cmd,采煤队</t>
-  </si>
-  <si>
-    <t>采煤队</t>
-  </si>
-  <si>
-    <t>003004</t>
-  </si>
-  <si>
-    <t>001,xlmy,鑫隆煤业</t>
-  </si>
-  <si>
-    <t>7ee2dcebe020b54bbc9ee4cc15538606</t>
-  </si>
-  <si>
-    <t>胡勤康</t>
-  </si>
-  <si>
-    <t>955bb98030d111f095ae4cd98fac570d</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>a65aa3ea057a4536a883b6b0f264ca34</t>
-  </si>
-  <si>
-    <t>004003,jsb,技术部</t>
-  </si>
-  <si>
-    <t>技术部</t>
-  </si>
-  <si>
-    <t>004003</t>
-  </si>
-  <si>
-    <t>a77ffbda7ed84370aa8a0e619740e01f</t>
-  </si>
-  <si>
-    <t>001001007,cmgzmqmg,采煤工作面清煤工</t>
-  </si>
-  <si>
-    <t>采煤工作面清煤工</t>
-  </si>
-  <si>
-    <t>001001007</t>
-  </si>
-  <si>
-    <t>a7ed97511497410b9c4d54d361143278</t>
-  </si>
-  <si>
-    <t>001001012,wcl8yy fbcyjldszjbycsj,WCL8YY 防爆柴油机履带式支架搬运车司机</t>
-  </si>
-  <si>
-    <t>WCL8YY 防爆柴油机履带式支架搬运车司机</t>
-  </si>
-  <si>
-    <t>001001012</t>
-  </si>
-  <si>
-    <t>a9c9e12f3d344664b58f222019c1b347</t>
-  </si>
-  <si>
-    <t>001002001,bz,班长</t>
-  </si>
-  <si>
-    <t>班长</t>
-  </si>
-  <si>
-    <t>001002001</t>
-  </si>
-  <si>
-    <t>001007,cc,抽采</t>
-  </si>
-  <si>
-    <t>001007</t>
-  </si>
-  <si>
-    <t>ac4085c13f67404799cb2eae64617a3e</t>
-  </si>
-  <si>
-    <t>001005002,wsy,瓦斯员</t>
-  </si>
-  <si>
-    <t>瓦斯员</t>
-  </si>
-  <si>
-    <t>001005002</t>
-  </si>
-  <si>
-    <t>ac43e2c35aba4da6b3398a9fc7de455b</t>
-  </si>
-  <si>
-    <t>001001008,cmgzmzzj、ysjsj,采煤工作面转载机、运输机司机</t>
-  </si>
-  <si>
-    <t>采煤工作面转载机、运输机司机</t>
-  </si>
-  <si>
-    <t>001001008</t>
-  </si>
-  <si>
-    <t>b26cd90198364f09a651458554588911</t>
-  </si>
-  <si>
-    <t>004008,aqjgb,安全监管部</t>
-  </si>
-  <si>
-    <t>安全监管部</t>
-  </si>
-  <si>
-    <t>004008</t>
-  </si>
-  <si>
-    <t>b29bf04cc9904ccabf97cdb75c913b16</t>
-  </si>
-  <si>
-    <t>001003006,jxdqg,井下电钳工</t>
-  </si>
-  <si>
-    <t>井下电钳工</t>
-  </si>
-  <si>
-    <t>001003006</t>
-  </si>
-  <si>
-    <t>001009,dmjdd,地面机电队</t>
-  </si>
-  <si>
-    <t>001009</t>
-  </si>
-  <si>
-    <t>b9f12740934a458c81591c233ec6a46c</t>
-  </si>
-  <si>
-    <t>001009011,fdgjxlg,风动工具修理工</t>
-  </si>
-  <si>
-    <t>风动工具修理工</t>
-  </si>
-  <si>
-    <t>001009011</t>
-  </si>
-  <si>
-    <t>ba158726889b412e9a4083a512e96674</t>
-  </si>
-  <si>
-    <t>003008,aqy,安全员</t>
-  </si>
-  <si>
-    <t>安全员</t>
-  </si>
-  <si>
-    <t>003008</t>
-  </si>
-  <si>
-    <t>001003,ys,运输</t>
-  </si>
-  <si>
-    <t>001003</t>
-  </si>
-  <si>
-    <t>bcf95c5c14d8458bb2e13338c1821e83</t>
-  </si>
-  <si>
-    <t>004004,scjsb,生产技术部</t>
-  </si>
-  <si>
-    <t>生产技术部</t>
-  </si>
-  <si>
-    <t>004004</t>
-  </si>
-  <si>
-    <t>003,hamy,惠安煤业</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>004,mygs,煤业公司</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>c12aa4ec5119436c90caa20d169adeba</t>
-  </si>
-  <si>
-    <t>001002002,jjjsj,掘进机司机</t>
-  </si>
-  <si>
-    <t>掘进机司机</t>
-  </si>
-  <si>
-    <t>001002002</t>
-  </si>
-  <si>
-    <t>c33b9ddeda6141b79bffbb8582a67e4b</t>
-  </si>
-  <si>
-    <t>003009,jkzx,监控中心</t>
-  </si>
-  <si>
-    <t>监控中心</t>
-  </si>
-  <si>
-    <t>003009</t>
-  </si>
-  <si>
-    <t>001005,tf,通风</t>
-  </si>
-  <si>
-    <t>通风</t>
-  </si>
-  <si>
-    <t>001005</t>
-  </si>
-  <si>
     <t>c6f2b47c6fed41f4ae8f50a13a55f484</t>
   </si>
   <si>
@@ -1339,7 +1366,7 @@
     <t>001002004</t>
   </si>
   <si>
-    <t>002,rdmy,荣大煤业</t>
+    <t>002,rdmy,容大煤业</t>
   </si>
   <si>
     <t>abfcef062ac611ef8172000c29df3f58</t>
@@ -2684,7 +2711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH112"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -3367,7 +3394,7 @@
     </row>
     <row r="13" spans="1:34">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -3376,51 +3403,42 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q13" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="R13" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="S13" s="1">
-        <v>45766.8654661806</v>
-      </c>
-      <c r="T13" t="s">
-        <v>38</v>
-      </c>
-      <c r="U13" t="s">
-        <v>39</v>
-      </c>
-      <c r="V13" s="1">
-        <v>46113.3828641782</v>
+        <v>46260.7038009144</v>
       </c>
       <c r="AA13" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AB13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AC13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AE13" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AF13" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AH13" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:34">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -3429,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q14" t="s">
         <v>57</v>
@@ -3438,7 +3456,7 @@
         <v>58</v>
       </c>
       <c r="S14" s="1">
-        <v>45766.853570787</v>
+        <v>45766.8654661806</v>
       </c>
       <c r="T14" t="s">
         <v>38</v>
@@ -3447,16 +3465,16 @@
         <v>39</v>
       </c>
       <c r="V14" s="1">
-        <v>46113.3828634954</v>
+        <v>46113.3828641782</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="AB14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AC14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AE14" t="s">
         <v>52</v>
@@ -3465,15 +3483,15 @@
         <v>53</v>
       </c>
       <c r="AG14" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -3482,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Q15" t="s">
         <v>57</v>
@@ -3491,7 +3509,7 @@
         <v>58</v>
       </c>
       <c r="S15" s="1">
-        <v>45766.869810706</v>
+        <v>45766.853570787</v>
       </c>
       <c r="T15" t="s">
         <v>38</v>
@@ -3500,16 +3518,16 @@
         <v>39</v>
       </c>
       <c r="V15" s="1">
-        <v>46197.4601881597</v>
+        <v>46113.3828634954</v>
       </c>
       <c r="AA15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AB15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AC15" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AE15" t="s">
         <v>52</v>
@@ -3518,15 +3536,15 @@
         <v>53</v>
       </c>
       <c r="AG15" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AH15" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -3535,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Q16" t="s">
         <v>57</v>
@@ -3544,7 +3562,7 @@
         <v>58</v>
       </c>
       <c r="S16" s="1">
-        <v>45766.8700518982</v>
+        <v>45766.869810706</v>
       </c>
       <c r="T16" t="s">
         <v>38</v>
@@ -3553,16 +3571,16 @@
         <v>39</v>
       </c>
       <c r="V16" s="1">
-        <v>46197.4605118866</v>
+        <v>46197.4601881597</v>
       </c>
       <c r="AA16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AB16" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="AC16" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="AE16" t="s">
         <v>52</v>
@@ -3571,15 +3589,15 @@
         <v>53</v>
       </c>
       <c r="AG16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AH16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:34">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -3588,16 +3606,16 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="Q17" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R17" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S17" s="1">
-        <v>45975.6296753935</v>
+        <v>45766.8700518982</v>
       </c>
       <c r="T17" t="s">
         <v>38</v>
@@ -3606,33 +3624,33 @@
         <v>39</v>
       </c>
       <c r="V17" s="1">
-        <v>46113.3828666204</v>
+        <v>46197.4605118866</v>
       </c>
       <c r="AA17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AB17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AC17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AE17" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG17" t="s">
         <v>129</v>
       </c>
-      <c r="AF17" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>126</v>
-      </c>
       <c r="AH17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:34">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -3641,16 +3659,16 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q18" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R18" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S18" s="1">
-        <v>45766.8695022685</v>
+        <v>45975.6296753935</v>
       </c>
       <c r="T18" t="s">
         <v>38</v>
@@ -3659,33 +3677,33 @@
         <v>39</v>
       </c>
       <c r="V18" s="1">
-        <v>46197.4600699537</v>
+        <v>46113.3828666204</v>
       </c>
       <c r="AA18" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="AB18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AC18" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG18" t="s">
         <v>135</v>
       </c>
-      <c r="AE18" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>86</v>
-      </c>
       <c r="AH18" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:34">
       <c r="A19" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3694,16 +3712,16 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="Q19" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="R19" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="S19" s="1">
-        <v>45913.7040488194</v>
+        <v>45766.8695022685</v>
       </c>
       <c r="T19" t="s">
         <v>38</v>
@@ -3712,33 +3730,33 @@
         <v>39</v>
       </c>
       <c r="V19" s="1">
-        <v>46113.382866088</v>
+        <v>46197.4600699537</v>
       </c>
       <c r="AA19" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="AB19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AC19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AE19" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AF19" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AG19" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:34">
       <c r="A20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3747,45 +3765,51 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="Q20" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="R20" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="S20" s="1">
-        <v>45823.6796206829</v>
+        <v>45913.7040488194</v>
       </c>
       <c r="T20" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U20" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="V20" s="1">
-        <v>46109.4242055093</v>
+        <v>46113.382866088</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AB20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AC20" t="s">
-        <v>145</v>
+        <v>150</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>44</v>
       </c>
       <c r="AG20" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="AH20" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:34">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3794,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="Q21" t="s">
         <v>38</v>
@@ -3803,7 +3827,7 @@
         <v>39</v>
       </c>
       <c r="S21" s="1">
-        <v>45823.6788845139</v>
+        <v>45823.6796206829</v>
       </c>
       <c r="T21" t="s">
         <v>47</v>
@@ -3812,27 +3836,27 @@
         <v>48</v>
       </c>
       <c r="V21" s="1">
-        <v>46109.424205463</v>
+        <v>46109.4242055093</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AB21" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="AC21" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AG21" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="AH21" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3841,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Q22" t="s">
         <v>38</v>
@@ -3850,42 +3874,36 @@
         <v>39</v>
       </c>
       <c r="S22" s="1">
-        <v>46111.893420081</v>
+        <v>45823.6788845139</v>
       </c>
       <c r="T22" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="U22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="V22" s="1">
-        <v>46113.382861875</v>
+        <v>46109.424205463</v>
       </c>
       <c r="AA22" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="AB22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AC22" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="AG22" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3894,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Q23" t="s">
         <v>38</v>
@@ -3903,7 +3921,7 @@
         <v>39</v>
       </c>
       <c r="S23" s="1">
-        <v>46143.6453759954</v>
+        <v>46111.893420081</v>
       </c>
       <c r="T23" t="s">
         <v>38</v>
@@ -3912,16 +3930,16 @@
         <v>39</v>
       </c>
       <c r="V23" s="1">
-        <v>46143.6629495833</v>
+        <v>46113.382861875</v>
       </c>
       <c r="AA23" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="AB23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AC23" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AE23" t="s">
         <v>52</v>
@@ -3930,15 +3948,15 @@
         <v>53</v>
       </c>
       <c r="AG23" t="s">
-        <v>156</v>
+        <v>59</v>
       </c>
       <c r="AH23" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:34">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3947,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Q24" t="s">
         <v>38</v>
@@ -3956,16 +3974,25 @@
         <v>39</v>
       </c>
       <c r="S24" s="1">
-        <v>46197.4603743403</v>
+        <v>46143.6453759954</v>
+      </c>
+      <c r="T24" t="s">
+        <v>38</v>
+      </c>
+      <c r="U24" t="s">
+        <v>39</v>
+      </c>
+      <c r="V24" s="1">
+        <v>46143.6629495833</v>
       </c>
       <c r="AA24" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AB24" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AC24" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AE24" t="s">
         <v>52</v>
@@ -3974,15 +4001,15 @@
         <v>53</v>
       </c>
       <c r="AG24" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AH24" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:34">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3991,34 +4018,25 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="Q25" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R25" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S25" s="1">
-        <v>45766.4307205208</v>
-      </c>
-      <c r="T25" t="s">
-        <v>38</v>
-      </c>
-      <c r="U25" t="s">
-        <v>39</v>
-      </c>
-      <c r="V25" s="1">
-        <v>46113.3828619907</v>
+        <v>46197.4603743403</v>
       </c>
       <c r="AA25" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AB25" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC25" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AE25" t="s">
         <v>52</v>
@@ -4027,15 +4045,15 @@
         <v>53</v>
       </c>
       <c r="AG25" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AH25" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:34">
       <c r="A26" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -4044,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="Q26" t="s">
         <v>57</v>
@@ -4053,7 +4071,7 @@
         <v>58</v>
       </c>
       <c r="S26" s="1">
-        <v>45766.8533768982</v>
+        <v>45766.4307205208</v>
       </c>
       <c r="T26" t="s">
         <v>38</v>
@@ -4062,16 +4080,16 @@
         <v>39</v>
       </c>
       <c r="V26" s="1">
-        <v>46113.3828637037</v>
+        <v>46113.3828619907</v>
       </c>
       <c r="AA26" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="AB26" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AC26" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="AE26" t="s">
         <v>52</v>
@@ -4080,15 +4098,15 @@
         <v>53</v>
       </c>
       <c r="AG26" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:34">
       <c r="A27" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -4097,16 +4115,16 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q27" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R27" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S27" s="1">
-        <v>46092.6306821181</v>
+        <v>45766.8533768982</v>
       </c>
       <c r="T27" t="s">
         <v>38</v>
@@ -4115,16 +4133,16 @@
         <v>39</v>
       </c>
       <c r="V27" s="1">
-        <v>46113.3828647106</v>
+        <v>46113.3828637037</v>
       </c>
       <c r="AA27" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="AB27" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC27" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="AE27" t="s">
         <v>52</v>
@@ -4133,15 +4151,15 @@
         <v>53</v>
       </c>
       <c r="AG27" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="AH27" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:34">
       <c r="A28" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4150,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q28" t="s">
         <v>38</v>
@@ -4159,7 +4177,7 @@
         <v>39</v>
       </c>
       <c r="S28" s="1">
-        <v>46092.6342894676</v>
+        <v>46092.6306821181</v>
       </c>
       <c r="T28" t="s">
         <v>38</v>
@@ -4168,16 +4186,16 @@
         <v>39</v>
       </c>
       <c r="V28" s="1">
-        <v>46113.3828651273</v>
+        <v>46113.3828647106</v>
       </c>
       <c r="AA28" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="AB28" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AC28" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="AE28" t="s">
         <v>52</v>
@@ -4186,15 +4204,15 @@
         <v>53</v>
       </c>
       <c r="AG28" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="AH28" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:34">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -4203,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q29" t="s">
         <v>38</v>
@@ -4212,36 +4230,42 @@
         <v>39</v>
       </c>
       <c r="S29" s="1">
-        <v>45823.6766874653</v>
+        <v>46092.6342894676</v>
       </c>
       <c r="T29" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="U29" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="V29" s="1">
-        <v>46109.4242054051</v>
+        <v>46113.3828651273</v>
       </c>
       <c r="AA29" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AB29" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="AC29" t="s">
-        <v>181</v>
+        <v>187</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>53</v>
       </c>
       <c r="AG29" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="AH29" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:34">
       <c r="A30" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -4250,51 +4274,45 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="Q30" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R30" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S30" s="1">
-        <v>45766.4218543403</v>
+        <v>45823.6766874653</v>
       </c>
       <c r="T30" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="U30" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="V30" s="1">
-        <v>46113.3828616667</v>
+        <v>46109.4242054051</v>
       </c>
       <c r="AA30" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="AB30" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="AC30" t="s">
-        <v>185</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="AG30" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:34">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -4303,16 +4321,16 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q31" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R31" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S31" s="1">
-        <v>45975.6308477894</v>
+        <v>45766.4218543403</v>
       </c>
       <c r="T31" t="s">
         <v>38</v>
@@ -4321,33 +4339,33 @@
         <v>39</v>
       </c>
       <c r="V31" s="1">
-        <v>46113.3828669444</v>
+        <v>46113.3828616667</v>
       </c>
       <c r="AA31" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="AB31" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AC31" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AE31" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="AF31" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="AG31" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="AH31" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:34">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -4356,16 +4374,16 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q32" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R32" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S32" s="1">
-        <v>45766.8559363773</v>
+        <v>45975.6308477894</v>
       </c>
       <c r="T32" t="s">
         <v>38</v>
@@ -4374,33 +4392,33 @@
         <v>39</v>
       </c>
       <c r="V32" s="1">
-        <v>46113.3828638657</v>
+        <v>46113.3828669444</v>
       </c>
       <c r="AA32" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="AB32" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AC32" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AE32" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="AF32" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="AG32" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="AH32" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:34">
       <c r="A33" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -4409,57 +4427,66 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q33" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="R33" t="s">
-        <v>197</v>
+        <v>58</v>
       </c>
       <c r="S33" s="1">
-        <v>46164.463413125</v>
+        <v>45766.8559363773</v>
+      </c>
+      <c r="T33" t="s">
+        <v>38</v>
+      </c>
+      <c r="U33" t="s">
+        <v>39</v>
+      </c>
+      <c r="V33" s="1">
+        <v>46113.3828638657</v>
       </c>
       <c r="AA33" t="s">
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="AB33" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AC33" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AE33" t="s">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="AF33" t="s">
-        <v>202</v>
+        <v>53</v>
       </c>
       <c r="AG33" t="s">
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="AH33" t="s">
-        <v>203</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:34">
       <c r="A34" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
         <v>204</v>
       </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="Q34" t="s">
         <v>205</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>206</v>
-      </c>
-      <c r="R34" t="s">
-        <v>207</v>
       </c>
       <c r="S34" s="1">
         <v>45975.4513793518</v>
@@ -4474,39 +4501,39 @@
         <v>46113.382866412</v>
       </c>
       <c r="AA34" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AB34" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="AC34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AE34" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AF34" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AG34" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AH34" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:34">
       <c r="A35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
         <v>209</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>210</v>
       </c>
       <c r="Q35" t="s">
         <v>38</v>
@@ -4530,10 +4557,10 @@
         <v>49</v>
       </c>
       <c r="AB35" t="s">
+        <v>210</v>
+      </c>
+      <c r="AC35" t="s">
         <v>211</v>
-      </c>
-      <c r="AC35" t="s">
-        <v>212</v>
       </c>
       <c r="AE35" t="s">
         <v>52</v>
@@ -4550,16 +4577,16 @@
     </row>
     <row r="36" spans="1:34">
       <c r="A36" t="s">
+        <v>212</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
         <v>213</v>
-      </c>
-      <c r="C36">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36" t="s">
-        <v>214</v>
       </c>
       <c r="Q36" t="s">
         <v>57</v>
@@ -4580,13 +4607,13 @@
         <v>46113.3828639699</v>
       </c>
       <c r="AA36" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AB36" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC36" t="s">
         <v>215</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>216</v>
       </c>
       <c r="AE36" t="s">
         <v>52</v>
@@ -4595,24 +4622,24 @@
         <v>53</v>
       </c>
       <c r="AG36" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AH36" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:34">
       <c r="A37" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
         <v>217</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37" t="s">
-        <v>218</v>
       </c>
       <c r="Q37" t="s">
         <v>38</v>
@@ -4636,10 +4663,10 @@
         <v>65</v>
       </c>
       <c r="AB37" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC37" t="s">
         <v>219</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>220</v>
       </c>
       <c r="AE37" t="s">
         <v>52</v>
@@ -4656,16 +4683,16 @@
     </row>
     <row r="38" spans="1:34">
       <c r="A38" t="s">
+        <v>220</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
         <v>221</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" t="s">
-        <v>222</v>
       </c>
       <c r="Q38" t="s">
         <v>47</v>
@@ -4689,10 +4716,10 @@
         <v>59</v>
       </c>
       <c r="AB38" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC38" t="s">
         <v>223</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>224</v>
       </c>
       <c r="AE38" t="s">
         <v>52</v>
@@ -4709,16 +4736,16 @@
     </row>
     <row r="39" spans="1:34">
       <c r="A39" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
         <v>225</v>
-      </c>
-      <c r="C39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39" t="s">
-        <v>226</v>
       </c>
       <c r="Q39" t="s">
         <v>38</v>
@@ -4739,39 +4766,39 @@
         <v>46113.3828668866</v>
       </c>
       <c r="AA39" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AB39" t="s">
+        <v>226</v>
+      </c>
+      <c r="AC39" t="s">
         <v>227</v>
       </c>
-      <c r="AC39" t="s">
-        <v>228</v>
-      </c>
       <c r="AE39" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AF39" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AG39" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AH39" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:34">
       <c r="A40" t="s">
+        <v>228</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
         <v>229</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40" t="s">
-        <v>230</v>
       </c>
       <c r="Q40" t="s">
         <v>57</v>
@@ -4792,13 +4819,13 @@
         <v>46113.3828636574</v>
       </c>
       <c r="AA40" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AB40" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC40" t="s">
         <v>231</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>232</v>
       </c>
       <c r="AE40" t="s">
         <v>52</v>
@@ -4807,10 +4834,10 @@
         <v>53</v>
       </c>
       <c r="AG40" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AH40" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:34">
@@ -4824,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q41" t="s">
         <v>38</v>
@@ -4851,7 +4878,7 @@
         <v>54</v>
       </c>
       <c r="AC41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE41" t="s">
         <v>52</v>
@@ -4868,16 +4895,16 @@
     </row>
     <row r="42" spans="1:34">
       <c r="A42" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
         <v>235</v>
-      </c>
-      <c r="C42">
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42" t="s">
-        <v>236</v>
       </c>
       <c r="Q42" t="s">
         <v>38</v>
@@ -4901,10 +4928,10 @@
         <v>96</v>
       </c>
       <c r="AB42" t="s">
+        <v>236</v>
+      </c>
+      <c r="AC42" t="s">
         <v>237</v>
-      </c>
-      <c r="AC42" t="s">
-        <v>238</v>
       </c>
       <c r="AE42" t="s">
         <v>52</v>
@@ -4921,16 +4948,16 @@
     </row>
     <row r="43" spans="1:34">
       <c r="A43" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
         <v>239</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43" t="s">
-        <v>240</v>
       </c>
       <c r="Q43" t="s">
         <v>38</v>
@@ -4951,13 +4978,13 @@
         <v>46113.3828630787</v>
       </c>
       <c r="AA43" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AB43" t="s">
+        <v>240</v>
+      </c>
+      <c r="AC43" t="s">
         <v>241</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>242</v>
       </c>
       <c r="AE43" t="s">
         <v>52</v>
@@ -4966,24 +4993,24 @@
         <v>53</v>
       </c>
       <c r="AG43" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AH43" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:34">
       <c r="A44" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
         <v>243</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44" t="s">
-        <v>244</v>
       </c>
       <c r="Q44" t="s">
         <v>57</v>
@@ -5004,13 +5031,13 @@
         <v>46113.3828640278</v>
       </c>
       <c r="AA44" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AB44" t="s">
+        <v>244</v>
+      </c>
+      <c r="AC44" t="s">
         <v>245</v>
-      </c>
-      <c r="AC44" t="s">
-        <v>246</v>
       </c>
       <c r="AE44" t="s">
         <v>52</v>
@@ -5019,24 +5046,24 @@
         <v>53</v>
       </c>
       <c r="AG44" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="AH44" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:34">
       <c r="A45" t="s">
+        <v>246</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
         <v>247</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45" t="s">
-        <v>248</v>
       </c>
       <c r="Q45" t="s">
         <v>38</v>
@@ -5057,13 +5084,13 @@
         <v>46113.3828626157</v>
       </c>
       <c r="AA45" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AB45" t="s">
+        <v>248</v>
+      </c>
+      <c r="AC45" t="s">
         <v>249</v>
-      </c>
-      <c r="AC45" t="s">
-        <v>250</v>
       </c>
       <c r="AE45" t="s">
         <v>52</v>
@@ -5072,24 +5099,24 @@
         <v>53</v>
       </c>
       <c r="AG45" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AH45" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:34">
       <c r="A46" t="s">
+        <v>250</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
         <v>251</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46" t="s">
-        <v>252</v>
       </c>
       <c r="Q46" t="s">
         <v>38</v>
@@ -5113,10 +5140,10 @@
         <v>65</v>
       </c>
       <c r="AB46" t="s">
+        <v>252</v>
+      </c>
+      <c r="AC46" t="s">
         <v>253</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>254</v>
       </c>
       <c r="AE46" t="s">
         <v>52</v>
@@ -5133,16 +5160,16 @@
     </row>
     <row r="47" spans="1:34">
       <c r="A47" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47" t="s">
         <v>255</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47" t="s">
-        <v>256</v>
       </c>
       <c r="Q47" t="s">
         <v>57</v>
@@ -5166,10 +5193,10 @@
         <v>59</v>
       </c>
       <c r="AB47" t="s">
+        <v>256</v>
+      </c>
+      <c r="AC47" t="s">
         <v>257</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>258</v>
       </c>
       <c r="AE47" t="s">
         <v>52</v>
@@ -5186,16 +5213,16 @@
     </row>
     <row r="48" spans="1:34">
       <c r="A48" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48" t="s">
         <v>259</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48" t="s">
-        <v>260</v>
       </c>
       <c r="Q48" t="s">
         <v>38</v>
@@ -5219,10 +5246,10 @@
         <v>65</v>
       </c>
       <c r="AB48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC48" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AE48" t="s">
         <v>52</v>
@@ -5239,16 +5266,16 @@
     </row>
     <row r="49" spans="1:34">
       <c r="A49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49" t="s">
         <v>262</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49" t="s">
-        <v>263</v>
       </c>
       <c r="Q49" t="s">
         <v>36</v>
@@ -5272,10 +5299,10 @@
         <v>40</v>
       </c>
       <c r="AB49" t="s">
+        <v>263</v>
+      </c>
+      <c r="AC49" t="s">
         <v>264</v>
-      </c>
-      <c r="AC49" t="s">
-        <v>265</v>
       </c>
       <c r="AE49" t="s">
         <v>43</v>
@@ -5301,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q50" t="s">
         <v>57</v>
@@ -5328,7 +5355,7 @@
         <v>104</v>
       </c>
       <c r="AC50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AE50" t="s">
         <v>52</v>
@@ -5345,16 +5372,16 @@
     </row>
     <row r="51" spans="1:34">
       <c r="A51" t="s">
+        <v>267</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
         <v>268</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51" t="s">
-        <v>269</v>
       </c>
       <c r="Q51" t="s">
         <v>57</v>
@@ -5378,10 +5405,10 @@
         <v>86</v>
       </c>
       <c r="AB51" t="s">
+        <v>269</v>
+      </c>
+      <c r="AC51" t="s">
         <v>270</v>
-      </c>
-      <c r="AC51" t="s">
-        <v>271</v>
       </c>
       <c r="AE51" t="s">
         <v>52</v>
@@ -5398,16 +5425,16 @@
     </row>
     <row r="52" spans="1:34">
       <c r="A52" t="s">
+        <v>271</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
         <v>272</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52" t="s">
-        <v>273</v>
       </c>
       <c r="Q52" t="s">
         <v>57</v>
@@ -5431,10 +5458,10 @@
         <v>71</v>
       </c>
       <c r="AB52" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC52" t="s">
         <v>274</v>
-      </c>
-      <c r="AC52" t="s">
-        <v>275</v>
       </c>
       <c r="AE52" t="s">
         <v>52</v>
@@ -5451,16 +5478,16 @@
     </row>
     <row r="53" spans="1:34">
       <c r="A53" t="s">
+        <v>275</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
         <v>276</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53" t="s">
-        <v>277</v>
       </c>
       <c r="Q53" t="s">
         <v>57</v>
@@ -5484,10 +5511,10 @@
         <v>59</v>
       </c>
       <c r="AB53" t="s">
+        <v>277</v>
+      </c>
+      <c r="AC53" t="s">
         <v>278</v>
-      </c>
-      <c r="AC53" t="s">
-        <v>279</v>
       </c>
       <c r="AE53" t="s">
         <v>52</v>
@@ -5504,16 +5531,16 @@
     </row>
     <row r="54" spans="1:34">
       <c r="A54" t="s">
+        <v>279</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" t="s">
         <v>280</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54" t="s">
-        <v>281</v>
       </c>
       <c r="Q54" t="s">
         <v>57</v>
@@ -5534,13 +5561,13 @@
         <v>46113.3828633449</v>
       </c>
       <c r="AA54" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AB54" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AC54" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="AE54" t="s">
         <v>52</v>
@@ -5549,24 +5576,24 @@
         <v>53</v>
       </c>
       <c r="AG54" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AH54" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:34">
       <c r="A55" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
         <v>282</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55" t="s">
-        <v>283</v>
       </c>
       <c r="Q55" t="s">
         <v>38</v>
@@ -5587,45 +5614,45 @@
         <v>46113.3828668287</v>
       </c>
       <c r="AA55" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AB55" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC55" t="s">
         <v>284</v>
       </c>
-      <c r="AC55" t="s">
-        <v>285</v>
-      </c>
       <c r="AE55" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AF55" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AG55" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AH55" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="56" spans="1:34">
       <c r="A56" t="s">
+        <v>285</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
         <v>286</v>
       </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56" t="s">
-        <v>287</v>
-      </c>
       <c r="Q56" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="R56" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="S56" s="1">
         <v>45914.6758047106</v>
@@ -5643,10 +5670,10 @@
         <v>40</v>
       </c>
       <c r="AB56" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="AC56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AE56" t="s">
         <v>43</v>
@@ -5663,16 +5690,16 @@
     </row>
     <row r="57" spans="1:34">
       <c r="A57" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
         <v>289</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57" t="s">
-        <v>290</v>
       </c>
       <c r="Q57" t="s">
         <v>38</v>
@@ -5693,39 +5720,39 @@
         <v>46113.3828667245</v>
       </c>
       <c r="AA57" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AB57" t="s">
+        <v>290</v>
+      </c>
+      <c r="AC57" t="s">
         <v>291</v>
       </c>
-      <c r="AC57" t="s">
-        <v>292</v>
-      </c>
       <c r="AE57" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AF57" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AG57" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AH57" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:34">
       <c r="A58" t="s">
+        <v>292</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
         <v>293</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58" t="s">
-        <v>294</v>
       </c>
       <c r="Q58" t="s">
         <v>38</v>
@@ -5746,13 +5773,13 @@
         <v>46113.3828627083</v>
       </c>
       <c r="AA58" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AB58" t="s">
+        <v>294</v>
+      </c>
+      <c r="AC58" t="s">
         <v>295</v>
-      </c>
-      <c r="AC58" t="s">
-        <v>296</v>
       </c>
       <c r="AE58" t="s">
         <v>52</v>
@@ -5761,24 +5788,24 @@
         <v>53</v>
       </c>
       <c r="AG58" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AH58" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="59" spans="1:34">
       <c r="A59" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
         <v>297</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59" t="s">
-        <v>298</v>
       </c>
       <c r="Q59" t="s">
         <v>57</v>
@@ -5802,10 +5829,10 @@
         <v>71</v>
       </c>
       <c r="AB59" t="s">
+        <v>298</v>
+      </c>
+      <c r="AC59" t="s">
         <v>299</v>
-      </c>
-      <c r="AC59" t="s">
-        <v>300</v>
       </c>
       <c r="AE59" t="s">
         <v>52</v>
@@ -5822,16 +5849,16 @@
     </row>
     <row r="60" spans="1:34">
       <c r="A60" t="s">
+        <v>300</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
         <v>301</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60" t="s">
-        <v>302</v>
       </c>
       <c r="Q60" t="s">
         <v>38</v>
@@ -5852,13 +5879,13 @@
         <v>46113.3828630324</v>
       </c>
       <c r="AA60" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AB60" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC60" t="s">
         <v>303</v>
-      </c>
-      <c r="AC60" t="s">
-        <v>304</v>
       </c>
       <c r="AE60" t="s">
         <v>52</v>
@@ -5867,51 +5894,51 @@
         <v>53</v>
       </c>
       <c r="AG60" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="AH60" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:34">
       <c r="A61" t="s">
+        <v>304</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61" t="s">
         <v>305</v>
       </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61" t="s">
+      <c r="Q61" t="s">
         <v>306</v>
       </c>
-      <c r="Q61" t="s">
-        <v>57</v>
-      </c>
       <c r="R61" t="s">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="S61" s="1">
-        <v>45766.8534689931</v>
+        <v>46287.7410151157</v>
       </c>
       <c r="T61" t="s">
-        <v>38</v>
+        <v>306</v>
       </c>
       <c r="U61" t="s">
-        <v>39</v>
+        <v>307</v>
       </c>
       <c r="V61" s="1">
-        <v>46113.3828635995</v>
+        <v>46287.7412014236</v>
       </c>
       <c r="AA61" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="AB61" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AC61" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AE61" t="s">
         <v>52</v>
@@ -5920,15 +5947,15 @@
         <v>53</v>
       </c>
       <c r="AG61" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:34">
       <c r="A62" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -5937,16 +5964,16 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q62" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R62" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S62" s="1">
-        <v>45975.6287043982</v>
+        <v>45766.8534689931</v>
       </c>
       <c r="T62" t="s">
         <v>38</v>
@@ -5955,33 +5982,33 @@
         <v>39</v>
       </c>
       <c r="V62" s="1">
-        <v>46113.3828664583</v>
+        <v>46113.3828635995</v>
       </c>
       <c r="AA62" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AB62" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AC62" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AE62" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="AF62" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="AG62" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="AH62" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:34">
       <c r="A63" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5990,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q63" t="s">
         <v>38</v>
@@ -5999,7 +6026,7 @@
         <v>39</v>
       </c>
       <c r="S63" s="1">
-        <v>45975.6309910301</v>
+        <v>45975.6287043982</v>
       </c>
       <c r="T63" t="s">
         <v>38</v>
@@ -6008,33 +6035,33 @@
         <v>39</v>
       </c>
       <c r="V63" s="1">
-        <v>46113.3828670023</v>
+        <v>46113.3828664583</v>
       </c>
       <c r="AA63" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AB63" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC63" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AE63" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AF63" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AG63" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AH63" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:34">
       <c r="A64" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6043,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q64" t="s">
         <v>38</v>
@@ -6052,7 +6079,7 @@
         <v>39</v>
       </c>
       <c r="S64" s="1">
-        <v>45975.629826169</v>
+        <v>45975.6309910301</v>
       </c>
       <c r="T64" t="s">
         <v>38</v>
@@ -6061,33 +6088,33 @@
         <v>39</v>
       </c>
       <c r="V64" s="1">
-        <v>46113.3828666782</v>
+        <v>46113.3828670023</v>
       </c>
       <c r="AA64" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AB64" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC64" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AE64" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AF64" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="AG64" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="AH64" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:34">
       <c r="A65" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6096,51 +6123,51 @@
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q65" t="s">
+        <v>38</v>
+      </c>
+      <c r="R65" t="s">
+        <v>39</v>
+      </c>
+      <c r="S65" s="1">
+        <v>45975.629826169</v>
+      </c>
+      <c r="T65" t="s">
+        <v>38</v>
+      </c>
+      <c r="U65" t="s">
+        <v>39</v>
+      </c>
+      <c r="V65" s="1">
+        <v>46113.3828666782</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>325</v>
+      </c>
+      <c r="AE65" t="s">
         <v>138</v>
       </c>
-      <c r="R65" t="s">
+      <c r="AF65" t="s">
         <v>139</v>
       </c>
-      <c r="S65" s="1">
-        <v>45913.6995880324</v>
-      </c>
-      <c r="T65" t="s">
-        <v>38</v>
-      </c>
-      <c r="U65" t="s">
-        <v>39</v>
-      </c>
-      <c r="V65" s="1">
-        <v>46113.3828660417</v>
-      </c>
-      <c r="AA65" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB65" t="s">
-        <v>323</v>
-      </c>
-      <c r="AC65" t="s">
-        <v>324</v>
-      </c>
-      <c r="AE65" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF65" t="s">
-        <v>44</v>
-      </c>
       <c r="AG65" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="AH65" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:34">
       <c r="A66" t="s">
-        <v>81</v>
+        <v>326</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6149,104 +6176,104 @@
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q66" t="s">
-        <v>326</v>
+        <v>147</v>
       </c>
       <c r="R66" t="s">
-        <v>327</v>
+        <v>148</v>
       </c>
       <c r="S66" s="1">
-        <v>45773.4425984491</v>
+        <v>45913.6995880324</v>
       </c>
       <c r="T66" t="s">
+        <v>38</v>
+      </c>
+      <c r="U66" t="s">
+        <v>39</v>
+      </c>
+      <c r="V66" s="1">
+        <v>46113.3828660417</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB66" t="s">
         <v>328</v>
       </c>
-      <c r="U66" t="s">
-        <v>327</v>
-      </c>
-      <c r="V66" s="1">
-        <v>46139.6743711458</v>
-      </c>
-      <c r="AA66" t="s">
+      <c r="AC66" t="s">
         <v>329</v>
       </c>
-      <c r="AB66" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC66" t="s">
-        <v>330</v>
-      </c>
       <c r="AE66" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AF66" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AG66" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="AH66" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:34">
       <c r="A67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q67" t="s">
         <v>331</v>
       </c>
-      <c r="C67">
-        <v>0</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67" t="s">
+      <c r="R67" t="s">
         <v>332</v>
       </c>
-      <c r="Q67" t="s">
-        <v>38</v>
-      </c>
-      <c r="R67" t="s">
-        <v>39</v>
-      </c>
       <c r="S67" s="1">
-        <v>45975.6289335648</v>
+        <v>45773.4425984491</v>
       </c>
       <c r="T67" t="s">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="U67" t="s">
-        <v>39</v>
+        <v>332</v>
       </c>
       <c r="V67" s="1">
-        <v>46113.3828665162</v>
+        <v>46139.6743711458</v>
       </c>
       <c r="AA67" t="s">
-        <v>126</v>
+        <v>334</v>
       </c>
       <c r="AB67" t="s">
-        <v>333</v>
+        <v>53</v>
       </c>
       <c r="AC67" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AE67" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="AF67" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="AG67" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="AH67" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:34">
       <c r="A68" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6255,16 +6282,16 @@
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q68" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R68" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S68" s="1">
-        <v>45766.4211049884</v>
+        <v>45975.6289335648</v>
       </c>
       <c r="T68" t="s">
         <v>38</v>
@@ -6273,33 +6300,33 @@
         <v>39</v>
       </c>
       <c r="V68" s="1">
-        <v>46113.3828615162</v>
+        <v>46113.3828665162</v>
       </c>
       <c r="AA68" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="AB68" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AC68" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AE68" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="AF68" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="AG68" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="AH68" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:34">
       <c r="A69" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6308,16 +6335,16 @@
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q69" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="R69" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="S69" s="1">
-        <v>46110.6986765741</v>
+        <v>45766.4211049884</v>
       </c>
       <c r="T69" t="s">
         <v>38</v>
@@ -6326,16 +6353,16 @@
         <v>39</v>
       </c>
       <c r="V69" s="1">
-        <v>46113.3828617708</v>
+        <v>46113.3828615162</v>
       </c>
       <c r="AA69" t="s">
         <v>59</v>
       </c>
       <c r="AB69" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AC69" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AE69" t="s">
         <v>52</v>
@@ -6347,12 +6374,12 @@
         <v>59</v>
       </c>
       <c r="AH69" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:34">
       <c r="A70" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -6361,16 +6388,16 @@
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q70" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="R70" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="S70" s="1">
-        <v>45766.4308739583</v>
+        <v>46110.6986765741</v>
       </c>
       <c r="T70" t="s">
         <v>38</v>
@@ -6379,16 +6406,16 @@
         <v>39</v>
       </c>
       <c r="V70" s="1">
-        <v>46113.382862037</v>
+        <v>46113.3828617708</v>
       </c>
       <c r="AA70" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="AB70" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AC70" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AE70" t="s">
         <v>52</v>
@@ -6397,15 +6424,15 @@
         <v>53</v>
       </c>
       <c r="AG70" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="AH70" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:34">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>348</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -6414,16 +6441,16 @@
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q71" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R71" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S71" s="1">
-        <v>46092.6292927431</v>
+        <v>45766.4308739583</v>
       </c>
       <c r="T71" t="s">
         <v>38</v>
@@ -6432,16 +6459,16 @@
         <v>39</v>
       </c>
       <c r="V71" s="1">
-        <v>46113.3828643982</v>
+        <v>46113.382862037</v>
       </c>
       <c r="AA71" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AB71" t="s">
-        <v>99</v>
+        <v>350</v>
       </c>
       <c r="AC71" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AE71" t="s">
         <v>52</v>
@@ -6450,15 +6477,15 @@
         <v>53</v>
       </c>
       <c r="AG71" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AH71" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:34">
       <c r="A72" t="s">
-        <v>349</v>
+        <v>96</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -6467,16 +6494,16 @@
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q72" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R72" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S72" s="1">
-        <v>45766.8560651157</v>
+        <v>46092.6292927431</v>
       </c>
       <c r="T72" t="s">
         <v>38</v>
@@ -6485,16 +6512,16 @@
         <v>39</v>
       </c>
       <c r="V72" s="1">
-        <v>46113.3828639236</v>
+        <v>46113.3828643982</v>
       </c>
       <c r="AA72" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AB72" t="s">
-        <v>351</v>
+        <v>99</v>
       </c>
       <c r="AC72" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AE72" t="s">
         <v>52</v>
@@ -6503,15 +6530,15 @@
         <v>53</v>
       </c>
       <c r="AG72" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:34">
       <c r="A73" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6520,7 +6547,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q73" t="s">
         <v>57</v>
@@ -6529,7 +6556,7 @@
         <v>58</v>
       </c>
       <c r="S73" s="1">
-        <v>45766.4213900579</v>
+        <v>45766.8560651157</v>
       </c>
       <c r="T73" t="s">
         <v>38</v>
@@ -6538,16 +6565,16 @@
         <v>39</v>
       </c>
       <c r="V73" s="1">
-        <v>46113.3828615625</v>
+        <v>46113.3828639236</v>
       </c>
       <c r="AA73" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="AB73" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AC73" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AE73" t="s">
         <v>52</v>
@@ -6556,15 +6583,15 @@
         <v>53</v>
       </c>
       <c r="AG73" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="AH73" t="s">
-        <v>62</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:34">
       <c r="A74" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6573,16 +6600,16 @@
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q74" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R74" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S74" s="1">
-        <v>45975.6301351968</v>
+        <v>45766.4213900579</v>
       </c>
       <c r="T74" t="s">
         <v>38</v>
@@ -6591,33 +6618,33 @@
         <v>39</v>
       </c>
       <c r="V74" s="1">
-        <v>46113.3828667824</v>
+        <v>46113.3828615625</v>
       </c>
       <c r="AA74" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="AB74" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AC74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AE74" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="AF74" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="AG74" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="AH74" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:34">
       <c r="A75" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6626,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q75" t="s">
         <v>38</v>
@@ -6635,7 +6662,7 @@
         <v>39</v>
       </c>
       <c r="S75" s="1">
-        <v>46092.6268333218</v>
+        <v>45975.6301351968</v>
       </c>
       <c r="T75" t="s">
         <v>38</v>
@@ -6644,33 +6671,33 @@
         <v>39</v>
       </c>
       <c r="V75" s="1">
-        <v>46113.3828628704</v>
+        <v>46113.3828667824</v>
       </c>
       <c r="AA75" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="AB75" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AC75" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AE75" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="AF75" t="s">
-        <v>53</v>
+        <v>139</v>
       </c>
       <c r="AG75" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="AH75" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:34">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>366</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -6679,7 +6706,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q76" t="s">
         <v>38</v>
@@ -6688,7 +6715,7 @@
         <v>39</v>
       </c>
       <c r="S76" s="1">
-        <v>46092.631653993</v>
+        <v>46092.6268333218</v>
       </c>
       <c r="T76" t="s">
         <v>38</v>
@@ -6697,16 +6724,16 @@
         <v>39</v>
       </c>
       <c r="V76" s="1">
-        <v>46113.3828649653</v>
+        <v>46113.3828628704</v>
       </c>
       <c r="AA76" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AB76" t="s">
-        <v>68</v>
+        <v>368</v>
       </c>
       <c r="AC76" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AE76" t="s">
         <v>52</v>
@@ -6715,15 +6742,15 @@
         <v>53</v>
       </c>
       <c r="AG76" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AH76" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:34">
       <c r="A77" t="s">
-        <v>367</v>
+        <v>65</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -6732,7 +6759,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q77" t="s">
         <v>38</v>
@@ -6741,7 +6768,7 @@
         <v>39</v>
       </c>
       <c r="S77" s="1">
-        <v>46092.6339764699</v>
+        <v>46092.631653993</v>
       </c>
       <c r="T77" t="s">
         <v>38</v>
@@ -6750,16 +6777,16 @@
         <v>39</v>
       </c>
       <c r="V77" s="1">
-        <v>46113.3828655556</v>
+        <v>46113.3828649653</v>
       </c>
       <c r="AA77" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="AB77" t="s">
-        <v>369</v>
+        <v>68</v>
       </c>
       <c r="AC77" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AE77" t="s">
         <v>52</v>
@@ -6768,15 +6795,15 @@
         <v>53</v>
       </c>
       <c r="AG77" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:34">
       <c r="A78" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -6785,16 +6812,16 @@
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q78" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="R78" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="S78" s="1">
-        <v>45914.676162419</v>
+        <v>46092.6339764699</v>
       </c>
       <c r="T78" t="s">
         <v>38</v>
@@ -6803,33 +6830,33 @@
         <v>39</v>
       </c>
       <c r="V78" s="1">
-        <v>46113.38286625</v>
+        <v>46113.3828655556</v>
       </c>
       <c r="AA78" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AB78" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AC78" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AE78" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AF78" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AG78" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AH78" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:34">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>376</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -6838,16 +6865,16 @@
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q79" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="R79" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="S79" s="1">
-        <v>46092.6192540741</v>
+        <v>45914.676162419</v>
       </c>
       <c r="T79" t="s">
         <v>38</v>
@@ -6856,33 +6883,33 @@
         <v>39</v>
       </c>
       <c r="V79" s="1">
-        <v>46113.3828625579</v>
+        <v>46113.38286625</v>
       </c>
       <c r="AA79" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="AB79" t="s">
-        <v>159</v>
+        <v>378</v>
       </c>
       <c r="AC79" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AE79" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AF79" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AG79" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="AH79" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:34">
       <c r="A80" t="s">
-        <v>377</v>
+        <v>165</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -6891,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q80" t="s">
         <v>38</v>
@@ -6900,7 +6927,7 @@
         <v>39</v>
       </c>
       <c r="S80" s="1">
-        <v>45975.6293791435</v>
+        <v>46092.6192540741</v>
       </c>
       <c r="T80" t="s">
         <v>38</v>
@@ -6909,33 +6936,33 @@
         <v>39</v>
       </c>
       <c r="V80" s="1">
-        <v>46113.3828665741</v>
+        <v>46113.3828625579</v>
       </c>
       <c r="AA80" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="AB80" t="s">
-        <v>379</v>
+        <v>168</v>
       </c>
       <c r="AC80" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AE80" t="s">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="AF80" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="AG80" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="AH80" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="1:34">
       <c r="A81" t="s">
-        <v>40</v>
+        <v>382</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -6944,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q81" t="s">
         <v>38</v>
@@ -6953,7 +6980,7 @@
         <v>39</v>
       </c>
       <c r="S81" s="1">
-        <v>45821.3545735301</v>
+        <v>45975.6293791435</v>
       </c>
       <c r="T81" t="s">
         <v>38</v>
@@ -6962,27 +6989,33 @@
         <v>39</v>
       </c>
       <c r="V81" s="1">
-        <v>46113.3828658218</v>
+        <v>46113.3828665741</v>
       </c>
       <c r="AA81" t="s">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="AB81" t="s">
-        <v>44</v>
+        <v>384</v>
       </c>
       <c r="AC81" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AE81" t="s">
-        <v>43</v>
+        <v>138</v>
       </c>
       <c r="AF81" t="s">
-        <v>44</v>
+        <v>139</v>
+      </c>
+      <c r="AG81" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH81" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="82" spans="1:34">
       <c r="A82" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -6991,16 +7024,16 @@
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q82" t="s">
-        <v>206</v>
+        <v>38</v>
       </c>
       <c r="R82" t="s">
-        <v>207</v>
+        <v>39</v>
       </c>
       <c r="S82" s="1">
-        <v>45975.4454966088</v>
+        <v>45821.3545735301</v>
       </c>
       <c r="T82" t="s">
         <v>38</v>
@@ -7009,27 +7042,27 @@
         <v>39</v>
       </c>
       <c r="V82" s="1">
-        <v>46113.3828663542</v>
+        <v>46113.3828658218</v>
       </c>
       <c r="AA82" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AB82" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="AC82" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AE82" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="AF82" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:34">
       <c r="A83" t="s">
-        <v>385</v>
+        <v>135</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -7038,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q83" t="s">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="R83" t="s">
-        <v>58</v>
+        <v>206</v>
       </c>
       <c r="S83" s="1">
-        <v>45766.4309929167</v>
+        <v>45975.4454966088</v>
       </c>
       <c r="T83" t="s">
         <v>38</v>
@@ -7056,33 +7089,27 @@
         <v>39</v>
       </c>
       <c r="V83" s="1">
-        <v>46113.3828620949</v>
+        <v>46113.3828663542</v>
       </c>
       <c r="AA83" t="s">
-        <v>86</v>
+        <v>334</v>
       </c>
       <c r="AB83" t="s">
-        <v>387</v>
+        <v>140</v>
       </c>
       <c r="AC83" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AE83" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="AF83" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG83" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH83" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:34">
       <c r="A84" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -7091,16 +7118,16 @@
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q84" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="R84" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="S84" s="1">
-        <v>45914.6763910995</v>
+        <v>45766.4309929167</v>
       </c>
       <c r="T84" t="s">
         <v>38</v>
@@ -7109,33 +7136,33 @@
         <v>39</v>
       </c>
       <c r="V84" s="1">
-        <v>46113.3828662963</v>
+        <v>46113.3828620949</v>
       </c>
       <c r="AA84" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="AB84" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AC84" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AE84" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AF84" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AG84" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="AH84" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:34">
       <c r="A85" t="s">
-        <v>120</v>
+        <v>394</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -7144,16 +7171,16 @@
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q85" t="s">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="R85" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="S85" s="1">
-        <v>45766.8557322801</v>
+        <v>45914.6763910995</v>
       </c>
       <c r="T85" t="s">
         <v>38</v>
@@ -7162,33 +7189,33 @@
         <v>39</v>
       </c>
       <c r="V85" s="1">
-        <v>46113.3828638079</v>
+        <v>46113.3828662963</v>
       </c>
       <c r="AA85" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="AB85" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AC85" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AE85" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AF85" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AG85" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="AH85" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86" spans="1:34">
       <c r="A86" t="s">
-        <v>396</v>
+        <v>129</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -7197,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q86" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R86" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S86" s="1">
-        <v>46092.6294766782</v>
+        <v>45766.8557322801</v>
       </c>
       <c r="T86" t="s">
         <v>38</v>
@@ -7215,16 +7242,16 @@
         <v>39</v>
       </c>
       <c r="V86" s="1">
-        <v>46113.3828644445</v>
+        <v>46113.3828638079</v>
       </c>
       <c r="AA86" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="AB86" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
       <c r="AC86" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AE86" t="s">
         <v>52</v>
@@ -7233,15 +7260,15 @@
         <v>53</v>
       </c>
       <c r="AG86" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="AH86" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
     </row>
     <row r="87" spans="1:34">
       <c r="A87" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -7250,51 +7277,42 @@
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q87" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="R87" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="S87" s="1">
-        <v>46092.6309540394</v>
-      </c>
-      <c r="T87" t="s">
-        <v>38</v>
-      </c>
-      <c r="U87" t="s">
-        <v>39</v>
-      </c>
-      <c r="V87" s="1">
-        <v>46113.3828647569</v>
+        <v>46256.6554247801</v>
       </c>
       <c r="AA87" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AB87" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AC87" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AE87" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AF87" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="AG87" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="AH87" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:34">
       <c r="A88" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -7303,16 +7321,16 @@
         <v>0</v>
       </c>
       <c r="H88" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q88" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R88" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S88" s="1">
-        <v>45766.4163447801</v>
+        <v>46092.6294766782</v>
       </c>
       <c r="T88" t="s">
         <v>38</v>
@@ -7321,16 +7339,16 @@
         <v>39</v>
       </c>
       <c r="V88" s="1">
-        <v>46113.38286125</v>
+        <v>46113.3828644445</v>
       </c>
       <c r="AA88" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="AB88" t="s">
-        <v>405</v>
+        <v>269</v>
       </c>
       <c r="AC88" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AE88" t="s">
         <v>52</v>
@@ -7339,15 +7357,15 @@
         <v>53</v>
       </c>
       <c r="AG88" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="AH88" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="89" spans="1:34">
       <c r="A89" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7356,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q89" t="s">
         <v>38</v>
@@ -7365,7 +7383,7 @@
         <v>39</v>
       </c>
       <c r="S89" s="1">
-        <v>46092.6271841204</v>
+        <v>46092.6309540394</v>
       </c>
       <c r="T89" t="s">
         <v>38</v>
@@ -7374,16 +7392,16 @@
         <v>39</v>
       </c>
       <c r="V89" s="1">
-        <v>46113.3828629745</v>
+        <v>46113.3828647569</v>
       </c>
       <c r="AA89" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="AB89" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AC89" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AE89" t="s">
         <v>52</v>
@@ -7392,15 +7410,15 @@
         <v>53</v>
       </c>
       <c r="AG89" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="AH89" t="s">
-        <v>159</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:34">
       <c r="A90" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -7409,16 +7427,16 @@
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q90" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R90" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S90" s="1">
-        <v>46092.6298479398</v>
+        <v>45766.4163447801</v>
       </c>
       <c r="T90" t="s">
         <v>38</v>
@@ -7427,16 +7445,16 @@
         <v>39</v>
       </c>
       <c r="V90" s="1">
-        <v>46113.3828645486</v>
+        <v>46113.38286125</v>
       </c>
       <c r="AA90" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="AB90" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AC90" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AE90" t="s">
         <v>52</v>
@@ -7445,15 +7463,15 @@
         <v>53</v>
       </c>
       <c r="AG90" t="s">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="AH90" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:34">
       <c r="A91" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -7462,16 +7480,16 @@
         <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q91" t="s">
-        <v>328</v>
+        <v>38</v>
       </c>
       <c r="R91" t="s">
-        <v>327</v>
+        <v>39</v>
       </c>
       <c r="S91" s="1">
-        <v>45907.4227536111</v>
+        <v>46092.6271841204</v>
       </c>
       <c r="T91" t="s">
         <v>38</v>
@@ -7480,33 +7498,33 @@
         <v>39</v>
       </c>
       <c r="V91" s="1">
-        <v>46113.3828658796</v>
+        <v>46113.3828629745</v>
       </c>
       <c r="AA91" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="AB91" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AC91" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AE91" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AF91" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AG91" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="AH91" t="s">
-        <v>44</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" spans="1:34">
       <c r="A92" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -7515,16 +7533,16 @@
         <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q92" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R92" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S92" s="1">
-        <v>45766.4167195255</v>
+        <v>46092.6298479398</v>
       </c>
       <c r="T92" t="s">
         <v>38</v>
@@ -7533,16 +7551,16 @@
         <v>39</v>
       </c>
       <c r="V92" s="1">
-        <v>46113.3828613079</v>
+        <v>46113.3828645486</v>
       </c>
       <c r="AA92" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="AB92" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AC92" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AE92" t="s">
         <v>52</v>
@@ -7551,15 +7569,15 @@
         <v>53</v>
       </c>
       <c r="AG92" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="AH92" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:34">
       <c r="A93" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -7568,16 +7586,16 @@
         <v>0</v>
       </c>
       <c r="H93" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q93" t="s">
-        <v>38</v>
+        <v>333</v>
       </c>
       <c r="R93" t="s">
-        <v>39</v>
+        <v>332</v>
       </c>
       <c r="S93" s="1">
-        <v>46092.6312451042</v>
+        <v>45907.4227536111</v>
       </c>
       <c r="T93" t="s">
         <v>38</v>
@@ -7586,33 +7604,33 @@
         <v>39</v>
       </c>
       <c r="V93" s="1">
-        <v>46113.3828648611</v>
+        <v>46113.3828658796</v>
       </c>
       <c r="AA93" t="s">
-        <v>399</v>
+        <v>40</v>
       </c>
       <c r="AB93" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AC93" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AE93" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AF93" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AG93" t="s">
-        <v>399</v>
+        <v>40</v>
       </c>
       <c r="AH93" t="s">
-        <v>401</v>
+        <v>44</v>
       </c>
     </row>
     <row r="94" spans="1:34">
       <c r="A94" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -7621,7 +7639,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q94" t="s">
         <v>57</v>
@@ -7630,7 +7648,7 @@
         <v>58</v>
       </c>
       <c r="S94" s="1">
-        <v>45766.8524323727</v>
+        <v>45766.4167195255</v>
       </c>
       <c r="T94" t="s">
         <v>38</v>
@@ -7639,16 +7657,16 @@
         <v>39</v>
       </c>
       <c r="V94" s="1">
-        <v>46113.3828635532</v>
+        <v>46113.3828613079</v>
       </c>
       <c r="AA94" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="AB94" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AC94" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AE94" t="s">
         <v>52</v>
@@ -7657,15 +7675,15 @@
         <v>53</v>
       </c>
       <c r="AG94" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="AH94" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:34">
       <c r="A95" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -7674,16 +7692,16 @@
         <v>0</v>
       </c>
       <c r="H95" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q95" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R95" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S95" s="1">
-        <v>45766.8493701042</v>
+        <v>46092.6312451042</v>
       </c>
       <c r="T95" t="s">
         <v>38</v>
@@ -7692,16 +7710,16 @@
         <v>39</v>
       </c>
       <c r="V95" s="1">
-        <v>46113.3828621991</v>
+        <v>46113.3828648611</v>
       </c>
       <c r="AA95" t="s">
-        <v>86</v>
+        <v>408</v>
       </c>
       <c r="AB95" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AC95" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AE95" t="s">
         <v>52</v>
@@ -7710,15 +7728,15 @@
         <v>53</v>
       </c>
       <c r="AG95" t="s">
-        <v>86</v>
+        <v>408</v>
       </c>
       <c r="AH95" t="s">
-        <v>89</v>
+        <v>410</v>
       </c>
     </row>
     <row r="96" spans="1:34">
       <c r="A96" t="s">
-        <v>198</v>
+        <v>436</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -7727,16 +7745,16 @@
         <v>0</v>
       </c>
       <c r="H96" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q96" t="s">
-        <v>436</v>
+        <v>57</v>
       </c>
       <c r="R96" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S96" s="1">
-        <v>45773.7362038657</v>
+        <v>45766.8524323727</v>
       </c>
       <c r="T96" t="s">
         <v>38</v>
@@ -7745,27 +7763,33 @@
         <v>39</v>
       </c>
       <c r="V96" s="1">
-        <v>46113.3828657639</v>
+        <v>46113.3828635532</v>
       </c>
       <c r="AA96" t="s">
-        <v>329</v>
+        <v>119</v>
       </c>
       <c r="AB96" t="s">
-        <v>203</v>
+        <v>438</v>
       </c>
       <c r="AC96" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AE96" t="s">
-        <v>201</v>
+        <v>52</v>
       </c>
       <c r="AF96" t="s">
-        <v>202</v>
+        <v>53</v>
+      </c>
+      <c r="AG96" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH96" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="97" spans="1:34">
       <c r="A97" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -7774,7 +7798,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q97" t="s">
         <v>57</v>
@@ -7783,7 +7807,7 @@
         <v>58</v>
       </c>
       <c r="S97" s="1">
-        <v>45766.4188587384</v>
+        <v>45766.8493701042</v>
       </c>
       <c r="T97" t="s">
         <v>38</v>
@@ -7792,16 +7816,16 @@
         <v>39</v>
       </c>
       <c r="V97" s="1">
-        <v>46194.3474190972</v>
+        <v>46113.3828621991</v>
       </c>
       <c r="AA97" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="AB97" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AC97" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AE97" t="s">
         <v>52</v>
@@ -7810,15 +7834,15 @@
         <v>53</v>
       </c>
       <c r="AG97" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="AH97" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:34">
       <c r="A98" t="s">
-        <v>442</v>
+        <v>109</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -7827,51 +7851,45 @@
         <v>0</v>
       </c>
       <c r="H98" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q98" t="s">
-        <v>38</v>
+        <v>445</v>
       </c>
       <c r="R98" t="s">
         <v>39</v>
       </c>
       <c r="S98" s="1">
-        <v>46092.6296090394</v>
+        <v>45773.7362038657</v>
       </c>
       <c r="T98" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="U98" t="s">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="V98" s="1">
-        <v>46113.3828645023</v>
+        <v>46255.3809303241</v>
       </c>
       <c r="AA98" t="s">
-        <v>96</v>
+        <v>334</v>
       </c>
       <c r="AB98" t="s">
-        <v>444</v>
+        <v>113</v>
       </c>
       <c r="AC98" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AE98" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="AF98" t="s">
-        <v>53</v>
-      </c>
-      <c r="AG98" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH98" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
     </row>
     <row r="99" spans="1:34">
       <c r="A99" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -7880,16 +7898,16 @@
         <v>0</v>
       </c>
       <c r="H99" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q99" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R99" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S99" s="1">
-        <v>46092.6327640741</v>
+        <v>45766.4188587384</v>
       </c>
       <c r="T99" t="s">
         <v>38</v>
@@ -7898,16 +7916,16 @@
         <v>39</v>
       </c>
       <c r="V99" s="1">
-        <v>46113.3828653472</v>
+        <v>46194.3474190972</v>
       </c>
       <c r="AA99" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AB99" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AC99" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AE99" t="s">
         <v>52</v>
@@ -7916,15 +7934,15 @@
         <v>53</v>
       </c>
       <c r="AG99" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AH99" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:34">
       <c r="A100" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -7933,16 +7951,16 @@
         <v>0</v>
       </c>
       <c r="H100" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q100" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R100" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S100" s="1">
-        <v>45766.4310868634</v>
+        <v>46092.6296090394</v>
       </c>
       <c r="T100" t="s">
         <v>38</v>
@@ -7951,16 +7969,16 @@
         <v>39</v>
       </c>
       <c r="V100" s="1">
-        <v>46113.3828621412</v>
+        <v>46113.3828645023</v>
       </c>
       <c r="AA100" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AB100" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="AC100" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AE100" t="s">
         <v>52</v>
@@ -7969,15 +7987,15 @@
         <v>53</v>
       </c>
       <c r="AG100" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AH100" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:34">
       <c r="A101" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -7986,16 +8004,16 @@
         <v>0</v>
       </c>
       <c r="H101" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Q101" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="R101" t="s">
-        <v>139</v>
+        <v>39</v>
       </c>
       <c r="S101" s="1">
-        <v>45914.6759808218</v>
+        <v>46092.6327640741</v>
       </c>
       <c r="T101" t="s">
         <v>38</v>
@@ -8004,33 +8022,33 @@
         <v>39</v>
       </c>
       <c r="V101" s="1">
-        <v>46113.3828661921</v>
+        <v>46113.3828653472</v>
       </c>
       <c r="AA101" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AB101" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AC101" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AE101" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AF101" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AG101" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AH101" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:34">
       <c r="A102" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -8039,16 +8057,16 @@
         <v>0</v>
       </c>
       <c r="H102" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Q102" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R102" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S102" s="1">
-        <v>46092.6117104745</v>
+        <v>45766.4310868634</v>
       </c>
       <c r="T102" t="s">
         <v>38</v>
@@ -8057,16 +8075,16 @@
         <v>39</v>
       </c>
       <c r="V102" s="1">
-        <v>46113.3828613542</v>
+        <v>46113.3828621412</v>
       </c>
       <c r="AA102" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="AB102" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="AC102" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AE102" t="s">
         <v>52</v>
@@ -8075,15 +8093,15 @@
         <v>53</v>
       </c>
       <c r="AG102" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="AH102" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="103" spans="1:34">
       <c r="A103" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -8092,16 +8110,16 @@
         <v>0</v>
       </c>
       <c r="H103" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q103" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="R103" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="S103" s="1">
-        <v>46113.3821965046</v>
+        <v>45914.6759808218</v>
       </c>
       <c r="T103" t="s">
         <v>38</v>
@@ -8110,33 +8128,33 @@
         <v>39</v>
       </c>
       <c r="V103" s="1">
-        <v>46113.3828624537</v>
+        <v>46113.3828661921</v>
       </c>
       <c r="AA103" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="AB103" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AC103" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AE103" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="AF103" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AG103" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="AH103" t="s">
-        <v>165</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104" spans="1:34">
       <c r="A104" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -8145,7 +8163,7 @@
         <v>0</v>
       </c>
       <c r="H104" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q104" t="s">
         <v>38</v>
@@ -8154,7 +8172,7 @@
         <v>39</v>
       </c>
       <c r="S104" s="1">
-        <v>46092.6318672685</v>
+        <v>46092.6117104745</v>
       </c>
       <c r="T104" t="s">
         <v>38</v>
@@ -8163,16 +8181,16 @@
         <v>39</v>
       </c>
       <c r="V104" s="1">
-        <v>46113.3828650232</v>
+        <v>46113.3828613542</v>
       </c>
       <c r="AA104" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AB104" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AC104" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AE104" t="s">
         <v>52</v>
@@ -8181,15 +8199,15 @@
         <v>53</v>
       </c>
       <c r="AG104" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AH104" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:34">
       <c r="A105" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -8198,16 +8216,16 @@
         <v>0</v>
       </c>
       <c r="H105" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Q105" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R105" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S105" s="1">
-        <v>45766.8519781366</v>
+        <v>46113.3821965046</v>
       </c>
       <c r="T105" t="s">
         <v>38</v>
@@ -8216,16 +8234,16 @@
         <v>39</v>
       </c>
       <c r="V105" s="1">
-        <v>46113.3828633912</v>
+        <v>46113.3828624537</v>
       </c>
       <c r="AA105" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="AB105" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AC105" t="s">
-        <v>145</v>
+        <v>473</v>
       </c>
       <c r="AE105" t="s">
         <v>52</v>
@@ -8234,15 +8252,15 @@
         <v>53</v>
       </c>
       <c r="AG105" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="AH105" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
     </row>
     <row r="106" spans="1:34">
       <c r="A106" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -8251,16 +8269,16 @@
         <v>0</v>
       </c>
       <c r="H106" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q106" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R106" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S106" s="1">
-        <v>45766.4159825579</v>
+        <v>46092.6318672685</v>
       </c>
       <c r="T106" t="s">
         <v>38</v>
@@ -8269,16 +8287,16 @@
         <v>39</v>
       </c>
       <c r="V106" s="1">
-        <v>46113.3828611921</v>
+        <v>46113.3828650232</v>
       </c>
       <c r="AA106" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AB106" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AC106" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AE106" t="s">
         <v>52</v>
@@ -8287,15 +8305,15 @@
         <v>53</v>
       </c>
       <c r="AG106" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AH106" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:34">
       <c r="A107" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -8304,16 +8322,16 @@
         <v>0</v>
       </c>
       <c r="H107" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Q107" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R107" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S107" s="1">
-        <v>46092.6332853819</v>
+        <v>45766.8519781366</v>
       </c>
       <c r="T107" t="s">
         <v>38</v>
@@ -8322,16 +8340,16 @@
         <v>39</v>
       </c>
       <c r="V107" s="1">
-        <v>46113.3828653935</v>
+        <v>46113.3828633912</v>
       </c>
       <c r="AA107" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="AB107" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AC107" t="s">
-        <v>479</v>
+        <v>154</v>
       </c>
       <c r="AE107" t="s">
         <v>52</v>
@@ -8340,15 +8358,15 @@
         <v>53</v>
       </c>
       <c r="AG107" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="AH107" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
     </row>
     <row r="108" spans="1:34">
       <c r="A108" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -8357,16 +8375,16 @@
         <v>0</v>
       </c>
       <c r="H108" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q108" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R108" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="S108" s="1">
-        <v>46092.633740463</v>
+        <v>45766.4159825579</v>
       </c>
       <c r="T108" t="s">
         <v>38</v>
@@ -8375,16 +8393,16 @@
         <v>39</v>
       </c>
       <c r="V108" s="1">
-        <v>46113.3828654977</v>
+        <v>46113.3828611921</v>
       </c>
       <c r="AA108" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AB108" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AC108" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AE108" t="s">
         <v>52</v>
@@ -8393,15 +8411,15 @@
         <v>53</v>
       </c>
       <c r="AG108" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="AH108" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" spans="1:34">
       <c r="A109" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -8410,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q109" t="s">
         <v>38</v>
@@ -8419,7 +8437,7 @@
         <v>39</v>
       </c>
       <c r="S109" s="1">
-        <v>46092.6269772685</v>
+        <v>46092.6332853819</v>
       </c>
       <c r="T109" t="s">
         <v>38</v>
@@ -8428,16 +8446,16 @@
         <v>39</v>
       </c>
       <c r="V109" s="1">
-        <v>46113.3828629282</v>
+        <v>46113.3828653935</v>
       </c>
       <c r="AA109" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="AB109" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AC109" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AE109" t="s">
         <v>52</v>
@@ -8446,15 +8464,15 @@
         <v>53</v>
       </c>
       <c r="AG109" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="AH109" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="1:34">
       <c r="A110" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -8463,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Q110" t="s">
         <v>38</v>
@@ -8472,7 +8490,7 @@
         <v>39</v>
       </c>
       <c r="S110" s="1">
-        <v>46092.6265925347</v>
+        <v>46092.633740463</v>
       </c>
       <c r="T110" t="s">
         <v>38</v>
@@ -8481,16 +8499,16 @@
         <v>39</v>
       </c>
       <c r="V110" s="1">
-        <v>46113.3828628241</v>
+        <v>46113.3828654977</v>
       </c>
       <c r="AA110" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="AB110" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AC110" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AE110" t="s">
         <v>52</v>
@@ -8499,15 +8517,15 @@
         <v>53</v>
       </c>
       <c r="AG110" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="AH110" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:34">
       <c r="A111" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -8516,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="H111" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Q111" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R111" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S111" s="1">
-        <v>45766.8522970949</v>
+        <v>46092.6269772685</v>
       </c>
       <c r="T111" t="s">
         <v>38</v>
@@ -8534,16 +8552,16 @@
         <v>39</v>
       </c>
       <c r="V111" s="1">
-        <v>46113.3828634491</v>
+        <v>46113.3828629282</v>
       </c>
       <c r="AA111" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="AB111" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AC111" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AE111" t="s">
         <v>52</v>
@@ -8552,15 +8570,15 @@
         <v>53</v>
       </c>
       <c r="AG111" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="AH111" t="s">
-        <v>113</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112" spans="1:34">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>497</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -8569,16 +8587,16 @@
         <v>0</v>
       </c>
       <c r="H112" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Q112" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="R112" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="S112" s="1">
-        <v>45766.8517301736</v>
+        <v>46092.6265925347</v>
       </c>
       <c r="T112" t="s">
         <v>38</v>
@@ -8587,16 +8605,16 @@
         <v>39</v>
       </c>
       <c r="V112" s="1">
-        <v>46113.3828632407</v>
+        <v>46113.3828628241</v>
       </c>
       <c r="AA112" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="AB112" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AC112" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AE112" t="s">
         <v>52</v>
@@ -8605,9 +8623,115 @@
         <v>53</v>
       </c>
       <c r="AG112" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH112" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="113" spans="1:34">
+      <c r="A113" t="s">
+        <v>501</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>57</v>
+      </c>
+      <c r="R113" t="s">
+        <v>58</v>
+      </c>
+      <c r="S113" s="1">
+        <v>45766.8522970949</v>
+      </c>
+      <c r="T113" t="s">
+        <v>38</v>
+      </c>
+      <c r="U113" t="s">
+        <v>39</v>
+      </c>
+      <c r="V113" s="1">
+        <v>46113.3828634491</v>
+      </c>
+      <c r="AA113" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB113" t="s">
+        <v>503</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>504</v>
+      </c>
+      <c r="AE113" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF113" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG113" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH113" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:34">
+      <c r="A114" t="s">
+        <v>119</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>57</v>
+      </c>
+      <c r="R114" t="s">
+        <v>58</v>
+      </c>
+      <c r="S114" s="1">
+        <v>45766.8517301736</v>
+      </c>
+      <c r="T114" t="s">
+        <v>38</v>
+      </c>
+      <c r="U114" t="s">
+        <v>39</v>
+      </c>
+      <c r="V114" s="1">
+        <v>46113.3828632407</v>
+      </c>
+      <c r="AA114" t="s">
         <v>81</v>
       </c>
-      <c r="AH112" t="s">
+      <c r="AB114" t="s">
+        <v>506</v>
+      </c>
+      <c r="AC114" t="s">
+        <v>507</v>
+      </c>
+      <c r="AE114" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF114" t="s">
+        <v>53</v>
+      </c>
+      <c r="AG114" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH114" t="s">
         <v>53</v>
       </c>
     </row>
